--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_123_R13.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_123_R13.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.7844</v>
+        <v>9.568099999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2447</v>
+        <v>7.4989</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5398</v>
+        <v>2.0693</v>
       </c>
       <c r="G2" t="n">
         <v>6.3676</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0069</v>
+        <v>1.7906</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7389</v>
+        <v>0.5153</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7458</v>
+        <v>1.2753</v>
       </c>
       <c r="V2" t="n">
         <v>2.5697</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. HERNANGOMEZ</t>
+          <t>K. SLOUKAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.773</v>
+        <v>8.091100000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5275</v>
+        <v>4.8342</v>
       </c>
       <c r="F3" t="n">
-        <v>5.2455</v>
+        <v>3.2569</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3381</v>
+        <v>6.295</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9772</v>
+        <v>3.3372</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6391</v>
+        <v>2.9578</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.2841</v>
+        <v>4.8941</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9278</v>
+        <v>2.7728</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.2118</v>
+        <v>2.1212</v>
       </c>
       <c r="M3" t="n">
-        <v>1.6222</v>
+        <v>1.401</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0495</v>
+        <v>0.5644</v>
       </c>
       <c r="O3" t="n">
-        <v>1.5727</v>
+        <v>0.8366</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.4639</v>
+        <v>-1.1598</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>6.8988</v>
+        <v>1.028</v>
       </c>
       <c r="T3" t="n">
-        <v>4.2032</v>
+        <v>0.0277</v>
       </c>
       <c r="U3" t="n">
-        <v>2.6956</v>
+        <v>1.0003</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="W3" t="n">
         <v>1.0722</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. SLOUKAS</t>
+          <t>J. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>8.125299999999999</v>
+        <v>5.4969</v>
       </c>
       <c r="E4" t="n">
-        <v>5.0701</v>
+        <v>1.1251</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0552</v>
+        <v>4.3717</v>
       </c>
       <c r="G4" t="n">
-        <v>6.295</v>
+        <v>0.3381</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3372</v>
+        <v>0.9772</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9578</v>
+        <v>-0.6391</v>
       </c>
       <c r="J4" t="n">
-        <v>4.8941</v>
+        <v>-1.2841</v>
       </c>
       <c r="K4" t="n">
-        <v>2.7728</v>
+        <v>0.9278</v>
       </c>
       <c r="L4" t="n">
-        <v>2.1212</v>
+        <v>-2.2118</v>
       </c>
       <c r="M4" t="n">
-        <v>1.401</v>
+        <v>1.6222</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5644</v>
+        <v>0.0495</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8366</v>
+        <v>1.5727</v>
       </c>
       <c r="P4" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1598</v>
+        <v>-0.4639</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0622</v>
+        <v>3.6227</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2636</v>
+        <v>1.8009</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7987</v>
+        <v>1.8218</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="W4" t="n">
         <v>1.0722</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5268</v>
+        <v>3.6111</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1695</v>
+        <v>1.2875</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3573</v>
+        <v>2.3237</v>
       </c>
       <c r="G5" t="n">
         <v>3.3998</v>
@@ -844,13 +844,13 @@
         <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5909</v>
+        <v>0.6752</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0351</v>
+        <v>0.0828</v>
       </c>
       <c r="U5" t="n">
-        <v>0.626</v>
+        <v>0.5924</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2618</v>
+        <v>2.7664</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4139</v>
+        <v>1.0784</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8479</v>
+        <v>1.688</v>
       </c>
       <c r="G6" t="n">
         <v>2.8941</v>
@@ -922,13 +922,13 @@
         <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3677</v>
+        <v>1.8723</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0474</v>
+        <v>0.7119</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3203</v>
+        <v>1.1604</v>
       </c>
       <c r="V6" t="n">
         <v>-1.0722</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1781</v>
+        <v>2.1045</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6676</v>
+        <v>1.4933</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5104</v>
+        <v>0.6112</v>
       </c>
       <c r="G7" t="n">
         <v>1.2147</v>
@@ -1000,13 +1000,13 @@
         <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2675</v>
+        <v>1.194</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4481</v>
+        <v>0.3776</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7156</v>
+        <v>0.8164</v>
       </c>
       <c r="V7" t="n">
         <v>-0.5361</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1246</v>
+        <v>0.2196</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1542</v>
+        <v>-0.8436</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0296</v>
+        <v>1.0632</v>
       </c>
       <c r="G8" t="n">
         <v>0.866</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1718</v>
+        <v>0.516</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.224</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3958</v>
+        <v>0.4294</v>
       </c>
       <c r="V8" t="n">
         <v>-0.9304</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. FARIED</t>
+          <t>A. SAMODUROV</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3765</v>
+        <v>-0.541</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6529</v>
+        <v>0.0013</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2763</v>
+        <v>-0.5423</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0866</v>
+        <v>-0.3941</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0038</v>
+        <v>-0.9026999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5981</v>
+        <v>-0.1614</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4509</v>
+        <v>-0.1982</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1472</v>
+        <v>0.0368</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5115</v>
+        <v>-0.2327</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4547</v>
+        <v>-0.7045</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0568</v>
+        <v>0.4718</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8556</v>
+        <v>0.6959</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.5515</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>2.859</v>
+        <v>-0.3066</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6948</v>
+        <v>-0.3734</v>
       </c>
       <c r="U9" t="n">
-        <v>1.1642</v>
+        <v>0.0668</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.4665</v>
+        <v>-0.5361</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3943</v>
+        <v>0.5361</v>
       </c>
       <c r="X9" t="n">
         <v>-1.0722</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. SAMODUROV</t>
+          <t>I. KOUZELOGLOU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7501</v>
+        <v>-1.081</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.07340000000000001</v>
+        <v>-1.0034</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6767</v>
+        <v>-0.0776</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3941</v>
+        <v>0.1161</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9026999999999999</v>
+        <v>-0.2353</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5086000000000001</v>
+        <v>0.3513</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1614</v>
+        <v>0.3057</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1982</v>
+        <v>0.2689</v>
       </c>
       <c r="L10" t="n">
         <v>0.0368</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2327</v>
+        <v>-0.1896</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7045</v>
+        <v>-0.5041</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4718</v>
+        <v>0.3145</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6959</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5157</v>
+        <v>-0.0373</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4481</v>
+        <v>-0.1494</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0677</v>
+        <v>0.112</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. KOUZELOGLOU</t>
+          <t>M. GRIGONIS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2229</v>
+        <v>-1.194</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0781</v>
+        <v>-1.1164</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1448</v>
+        <v>-0.0776</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1161</v>
+        <v>-0.9993</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2353</v>
+        <v>-0.4873</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3513</v>
+        <v>-0.512</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3057</v>
+        <v>-0.967</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2689</v>
+        <v>0.0168</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0368</v>
+        <v>-0.9838</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1896</v>
+        <v>-0.0323</v>
       </c>
       <c r="N11" t="n">
         <v>-0.5041</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3145</v>
+        <v>0.4718</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1792</v>
+        <v>-0.1946</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.224</v>
+        <v>-0.1494</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0448</v>
+        <v>-0.0452</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. GRIGONIS</t>
+          <t>K. FARIED</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3359</v>
+        <v>-1.2619</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.191</v>
+        <v>-1.4038</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1448</v>
+        <v>0.1419</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.9993</v>
+        <v>0.0866</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4873</v>
+        <v>-0.0038</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.512</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.967</v>
+        <v>0.5981</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0168</v>
+        <v>0.4509</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.9838</v>
+        <v>0.1472</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0323</v>
+        <v>-0.5115</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5041</v>
+        <v>-0.4547</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4718</v>
+        <v>-0.0568</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3365</v>
+        <v>1.9736</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.224</v>
+        <v>0.9438</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1125</v>
+        <v>1.0297</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.4665</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.2915</v>
+        <v>-5.4852</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.3857</v>
+        <v>-3.6466</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.9058</v>
+        <v>-1.8386</v>
       </c>
       <c r="G13" t="n">
         <v>-2.5452</v>
@@ -1468,13 +1468,13 @@
         <v>0.232</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2618</v>
+        <v>0.5445</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3655</v>
+        <v>0.3736</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1037</v>
+        <v>0.1709</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8608</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>21.5479</v>
+        <v>22.2946</v>
       </c>
       <c r="E14" t="n">
-        <v>8.558000000000002</v>
+        <v>9.304899999999998</v>
       </c>
       <c r="F14" t="n">
-        <v>12.9899</v>
+        <v>12.9898</v>
       </c>
       <c r="G14" t="n">
-        <v>17.63939999999999</v>
+        <v>17.6394</v>
       </c>
       <c r="H14" t="n">
         <v>5.8278</v>
@@ -1531,10 +1531,10 @@
         <v>4.0888</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.277100000000001</v>
+        <v>-4.2771</v>
       </c>
       <c r="O14" t="n">
-        <v>8.3659</v>
+        <v>8.365899999999998</v>
       </c>
       <c r="P14" t="n">
         <v>-5.7988</v>
@@ -1546,19 +1546,19 @@
         <v>8.118499999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>11.9316</v>
+        <v>12.6784</v>
       </c>
       <c r="T14" t="n">
-        <v>3.5013</v>
+        <v>4.2479</v>
       </c>
       <c r="U14" t="n">
-        <v>8.430299999999999</v>
+        <v>8.430199999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.2241</v>
+        <v>-2.224099999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>5.423100000000002</v>
+        <v>5.423100000000001</v>
       </c>
       <c r="X14" t="n">
         <v>-7.647200000000002</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5197</v>
+        <v>1.0143</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5455</v>
+        <v>0.0736</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.9407</v>
       </c>
       <c r="G15" t="n">
         <v>-0.855</v>
@@ -1624,13 +1624,13 @@
         <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1428</v>
+        <v>-0.3626</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1889</v>
+        <v>-0.2829</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0461</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>1.0722</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4462</v>
+        <v>0.632</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4155</v>
+        <v>0.7693</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0307</v>
+        <v>-0.1374</v>
       </c>
       <c r="G16" t="n">
         <v>-2.3409</v>
@@ -1702,13 +1702,13 @@
         <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2851</v>
+        <v>-0.0993</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8215</v>
+        <v>-0.4676</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5364</v>
+        <v>0.3684</v>
       </c>
       <c r="V16" t="n">
         <v>2.1444</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1213</v>
+        <v>0.1391</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2666</v>
+        <v>-0.9127</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3879</v>
+        <v>1.0518</v>
       </c>
       <c r="G17" t="n">
         <v>-0.716</v>
@@ -1780,13 +1780,13 @@
         <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7863</v>
+        <v>-0.7685999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3443</v>
+        <v>-0.9903999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5579</v>
+        <v>0.2219</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1012</v>
+        <v>-0.2306</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4871</v>
+        <v>0.1333</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5884</v>
+        <v>-0.3639</v>
       </c>
       <c r="G18" t="n">
         <v>-0.6153999999999999</v>
@@ -1858,13 +1858,13 @@
         <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7178</v>
+        <v>-0.8472</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1098</v>
+        <v>-0.4637</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.608</v>
+        <v>-0.3835</v>
       </c>
       <c r="V18" t="n">
         <v>0.5361</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. MUURINEN</t>
+          <t>A. POKUSEVSKI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3174</v>
+        <v>-0.2335</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1494</v>
+        <v>-0.9842</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.168</v>
+        <v>0.7507</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0108</v>
+        <v>-0.1913</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.168</v>
+        <v>0.9664</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1573</v>
+        <v>-1.1578</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.3553</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1.378</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-1.7334</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0108</v>
+        <v>0.164</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.168</v>
+        <v>-0.4116</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1573</v>
+        <v>0.5756</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3066</v>
+        <v>-1.1323</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1494</v>
+        <v>-0.6289</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1573</v>
+        <v>-0.5034</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. POKUSEVSKI</t>
+          <t>M. MUURINEN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3743</v>
+        <v>-0.3174</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1022</v>
+        <v>-0.1494</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7279</v>
+        <v>-0.168</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1913</v>
+        <v>-0.0108</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9664</v>
+        <v>-0.168</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1578</v>
+        <v>0.1573</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3553</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1.378</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.7334</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.164</v>
+        <v>-0.0108</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4116</v>
+        <v>-0.168</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5756</v>
+        <v>0.1573</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2731</v>
+        <v>-0.3066</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7468</v>
+        <v>-0.1494</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5263</v>
+        <v>-0.1573</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5033</v>
+        <v>-1.4862</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2755</v>
+        <v>-1.1576</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2278</v>
+        <v>-0.3286</v>
       </c>
       <c r="G21" t="n">
         <v>-1.6681</v>
@@ -2092,13 +2092,13 @@
         <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5311</v>
+        <v>-0.514</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5228</v>
+        <v>-0.4048</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0083</v>
+        <v>-0.1092</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. BROWN</t>
+          <t>V. MARINKOVIC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2611</v>
+        <v>-2.1398</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.302</v>
+        <v>-0.4523</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9591</v>
+        <v>-1.6875</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9606</v>
+        <v>-1.9782</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.0312</v>
+        <v>-0.1078</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0706</v>
+        <v>-1.8704</v>
       </c>
       <c r="J22" t="n">
-        <v>1.2633</v>
+        <v>-0.4908</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3894</v>
+        <v>1.0083</v>
       </c>
       <c r="L22" t="n">
-        <v>1.6527</v>
+        <v>-1.4991</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.2239</v>
+        <v>-1.4874</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.6418</v>
+        <v>-1.1161</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5821</v>
+        <v>-0.3713</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.9294</v>
+        <v>-1.4811</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.782</v>
+        <v>-1.0337</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1474</v>
+        <v>-0.4474</v>
       </c>
       <c r="V22" t="n">
-        <v>1.3247</v>
+        <v>-0.5361</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="X22" t="n">
-        <v>0.7886</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V. MARINKOVIC</t>
+          <t>S. BROWN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8354</v>
+        <v>-2.256</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6882</v>
+        <v>-1.6559</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1473</v>
+        <v>-0.6002</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.9782</v>
+        <v>-0.9606</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1078</v>
+        <v>-2.0312</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.8704</v>
+        <v>1.0706</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.4908</v>
+        <v>1.2633</v>
       </c>
       <c r="K23" t="n">
-        <v>1.0083</v>
+        <v>-0.3894</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.4991</v>
+        <v>1.6527</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.4874</v>
+        <v>-2.2239</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1161</v>
+        <v>-1.6418</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3713</v>
+        <v>-0.5821</v>
       </c>
       <c r="P23" t="n">
-        <v>1.8556</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.1767</v>
+        <v>-1.9244</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2696</v>
+        <v>-1.1358</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9071</v>
+        <v>-0.7885</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.5361</v>
+        <v>1.3247</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.6083</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.8799</v>
+        <v>-3.4867</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1196</v>
+        <v>-1.8837</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7603</v>
+        <v>-1.6031</v>
       </c>
       <c r="G24" t="n">
         <v>-1.6506</v>
@@ -2326,13 +2326,13 @@
         <v>1.6237</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.5515</v>
+        <v>-2.1583</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.7177</v>
+        <v>-1.4818</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8338</v>
+        <v>-0.6765</v>
       </c>
       <c r="V24" t="n">
         <v>-0.1418</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>T. JONES</t>
+          <t>J. PARKER</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.9539</v>
+        <v>-5.9709</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.7444</v>
+        <v>-3.5543</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.2095</v>
+        <v>-2.4166</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.1245</v>
+        <v>-5.528</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.8234</v>
+        <v>-2.1919</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3011</v>
+        <v>-3.3361</v>
       </c>
       <c r="J25" t="n">
-        <v>0.77</v>
+        <v>-2.5824</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0707</v>
+        <v>-0.6148</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6993</v>
+        <v>-1.9676</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.8945</v>
+        <v>-2.9456</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.8942</v>
+        <v>-1.5771</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.0004</v>
+        <v>-1.3684</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.5515</v>
+        <v>0.9278</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9278</v>
+        <v>2.0876</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1336</v>
+        <v>-0.9454</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0351</v>
+        <v>-0.8843</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0984</v>
+        <v>-0.0611</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.1444</v>
+        <v>-0.4254</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.1444</v>
+        <v>-1.4975</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J. PARKER</t>
+          <t>T. JONES</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.4085</v>
+        <v>-6.4257</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.7902</v>
+        <v>-3.2162</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.6183</v>
+        <v>-3.2095</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.528</v>
+        <v>-1.1245</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.1919</v>
+        <v>-0.8234</v>
       </c>
       <c r="I26" t="n">
-        <v>-3.3361</v>
+        <v>-0.3011</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.5824</v>
+        <v>0.77</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.6148</v>
+        <v>0.0707</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.9676</v>
+        <v>0.6993</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.9456</v>
+        <v>-1.8945</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.5771</v>
+        <v>-0.8942</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.3684</v>
+        <v>-1.0004</v>
       </c>
       <c r="P26" t="n">
+        <v>-2.5515</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-3.4793</v>
+      </c>
+      <c r="R26" t="n">
         <v>0.9278</v>
       </c>
-      <c r="Q26" t="n">
-        <v>-1.1598</v>
-      </c>
-      <c r="R26" t="n">
-        <v>2.0876</v>
-      </c>
       <c r="S26" t="n">
-        <v>-1.3829</v>
+        <v>-0.6054</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.1202</v>
+        <v>-0.507</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2627</v>
+        <v>-0.0984</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.4254</v>
+        <v>-2.1444</v>
       </c>
       <c r="W26" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.4975</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="27">
@@ -2515,19 +2515,19 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-21.5478</v>
+        <v>-20.7614</v>
       </c>
       <c r="E27" t="n">
-        <v>-12.99</v>
+        <v>-12.9901</v>
       </c>
       <c r="F27" t="n">
-        <v>-8.5579</v>
+        <v>-7.771599999999999</v>
       </c>
       <c r="G27" t="n">
         <v>-17.6394</v>
       </c>
       <c r="H27" t="n">
-        <v>-5.8278</v>
+        <v>-5.827800000000001</v>
       </c>
       <c r="I27" t="n">
         <v>-11.8115</v>
@@ -2551,28 +2551,28 @@
         <v>-3.4454</v>
       </c>
       <c r="P27" t="n">
-        <v>5.7989</v>
+        <v>5.798899999999999</v>
       </c>
       <c r="Q27" t="n">
-        <v>-8.118400000000001</v>
+        <v>-8.118399999999999</v>
       </c>
       <c r="R27" t="n">
         <v>13.9174</v>
       </c>
       <c r="S27" t="n">
-        <v>-11.9313</v>
+        <v>-11.1452</v>
       </c>
       <c r="T27" t="n">
         <v>-8.430299999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>-3.5011</v>
+        <v>-2.7147</v>
       </c>
       <c r="V27" t="n">
         <v>2.224</v>
       </c>
       <c r="W27" t="n">
-        <v>7.647200000000002</v>
+        <v>7.6472</v>
       </c>
       <c r="X27" t="n">
         <v>-5.4231</v>
